--- a/Resources/Review/Missing Variables Referenced in Rename Crosswalk.xlsx
+++ b/Resources/Review/Missing Variables Referenced in Rename Crosswalk.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B17"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -393,166 +393,118 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>disposition_facility_code</t>
+          <t>injury_county_city_wa_code</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2010,2016</t>
+          <t>2022,2023,2024</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>disposition_facility_name</t>
+          <t>injury_county_wa_code</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2010,2011,2012,2013,2014,2015</t>
+          <t>2022,2023,2024</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>funeral_home_code</t>
+          <t>residence_county_city_wa_code</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2022,2023,2024</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>funeral_home_name</t>
+          <t>residence_county_wa_code</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2010,2011,2012,2013,2014,2015</t>
+          <t>2022,2023,2024</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>injury_county_city_wa_code</t>
+          <t>time_of_death</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2022,2023,2024</t>
+          <t>2010,2013,2014,2015,2016,2017,2018,2019,2020,2021,2022,2023,2024</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>injury_county_wa_code</t>
+          <t>time_of_death_hour</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2022,2023,2024</t>
+          <t>2011,2012</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>residence_county_city_wa_code</t>
+          <t>time_of_death_minutes</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2022,2023,2024</t>
+          <t>2011,2012</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>residence_county_wa_code</t>
+          <t>time_of_injury</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2022,2023,2024</t>
+          <t>2010,2013,2014,2015,2016,2017,2018,2019,2020,2021,2022,2023,2024</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>time_of_death</t>
+          <t>time_of_injury_hour</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2010,2013,2014,2015,2016,2017,2018,2019,2020,2021,2022,2023,2024</t>
+          <t>2011,2012</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>time_of_death_hour</t>
+          <t>time_of_injury_minutes</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
-        <is>
-          <t>2011,2012</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>time_of_death_minutes</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>2011,2012</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>time_of_injury</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>2010,2013,2014,2015,2016,2017,2018,2019,2020,2021,2022,2023,2024</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>time_of_injury_hour</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>2011,2012</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>time_of_injury_minutes</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
         <is>
           <t>2011,2012</t>
         </is>

--- a/Resources/Review/Missing Variables Referenced in Rename Crosswalk.xlsx
+++ b/Resources/Review/Missing Variables Referenced in Rename Crosswalk.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -369,19 +369,19 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>death_county_city_wa_code</t>
+          <t>death_city_fips</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2022,2023,2024</t>
+          <t>2010,2011,2012,2013,2014,2015,2016,2017,2018,2019,2020,2021</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>death_county_wa_code</t>
+          <t>death_county_city_wa_code</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -393,19 +393,19 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>injury_county_city_wa_code</t>
+          <t>death_county_fips</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2022,2023,2024</t>
+          <t>2010,2011,2012,2013,2014,2015,2016,2017,2018,2019,2020,2021</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>injury_county_wa_code</t>
+          <t>death_county_wa_code</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -417,94 +417,190 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>residence_county_city_wa_code</t>
+          <t>injury_city_fips</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2022,2023,2024</t>
+          <t>2010,2011,2012,2013,2014,2015,2016,2017,2018,2019,2020,2021</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>residence_county_wa_code</t>
+          <t>injury_county</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2022,2023,2024</t>
+          <t>2010,2011,2012,2013,2014,2015</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>time_of_death</t>
+          <t>injury_county_city_wa_code</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2010,2013,2014,2015,2016,2017,2018,2019,2020,2021,2022,2023,2024</t>
+          <t>2022,2023,2024</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>time_of_death_hour</t>
+          <t>injury_county_fips</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2011,2012</t>
+          <t>2010,2011,2012,2013,2014,2015,2016,2017,2018,2019,2020,2021</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>time_of_death_minutes</t>
+          <t>injury_county_wa_code</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2011,2012</t>
+          <t>2022,2023,2024</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>time_of_injury</t>
+          <t>residence_city_fips</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2010,2013,2014,2015,2016,2017,2018,2019,2020,2021,2022,2023,2024</t>
+          <t>2010,2011,2012,2013,2014,2015</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>time_of_injury_hour</t>
+          <t>residence_county</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2011,2012</t>
+          <t>2010,2011,2012,2013,2014,2015</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>residence_county_city_wa_code</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2022,2023,2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>residence_county_fips</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2010,2011,2012,2013,2014,2015</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>residence_county_wa_code</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2022,2023,2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>time_of_death</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2010,2013,2014,2015,2016,2017,2018,2019,2020,2021,2022,2023,2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>time_of_death_hour</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2011,2012</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>time_of_death_minutes</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2011,2012</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>time_of_injury</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2010,2013,2014,2015,2016,2017,2018,2019,2020,2021,2022,2023,2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>time_of_injury_hour</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2011,2012</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
           <t>time_of_injury_minutes</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>2011,2012</t>
         </is>
